--- a/src/excel-data/shikoku.xlsx
+++ b/src/excel-data/shikoku.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/Cao Yuxuan/テストweb/findmyrailpass.net/src/excel-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9971C3A6-01E4-1F41-A360-3C492DD0A306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E66CFE0-9690-CB46-B146-F2122494285C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="1060" windowWidth="38400" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="shikoku周游券" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="162">
   <si>
     <t>sortOrder</t>
   </si>
@@ -98,25 +111,19 @@
   </si>
   <si>
     <t>bestFor</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>地铁</t>
-  </si>
-  <si>
-    <t>city</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>price_over65</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>price_under15</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>price_free</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>JRShikoku-FreePass</t>
@@ -161,9 +168,6 @@
     <t>週末乗り放題きっぷ</t>
   </si>
   <si>
-    <t>周末无限乘车券</t>
-  </si>
-  <si>
     <t>/images/coverage/JRShikoku-Weekend-Norihodai.png</t>
   </si>
   <si>
@@ -173,9 +177,6 @@
     <t>四国再発見早トクきっぷ</t>
   </si>
   <si>
-    <t>四国再发现早鸟优惠券</t>
-  </si>
-  <si>
     <t>/images/coverage/JRShikoku-Raihaku-Hayatoroku.png</t>
   </si>
   <si>
@@ -194,9 +195,6 @@
     <t>ことでんおんせん乗車入浴券</t>
   </si>
   <si>
-    <t>琴平温泉乘车入浴券</t>
-  </si>
-  <si>
     <t>/images/coverage/Kotoden-Onsen-Rail-Bathing-Ticket.png</t>
   </si>
   <si>
@@ -221,9 +219,6 @@
     <t>ことでん×NEWレオマワールドセットきっぷ</t>
   </si>
   <si>
-    <t>琴电×新レオマ世界套票</t>
-  </si>
-  <si>
     <t>/images/coverage/Kotoden-New-Reoma-World-Set-Kippu.png</t>
   </si>
   <si>
@@ -251,9 +246,6 @@
     <t>市内電車･郊外電車 1Dayチケット</t>
   </si>
   <si>
-    <t>伊予铁道市内电车·郊外电车1日票</t>
-  </si>
-  <si>
     <t>/images/coverage/Iyotetsu-City-Tram-Suburban-1Day.png</t>
   </si>
   <si>
@@ -263,9 +255,6 @@
     <t>市内電車･リムジンバス 1Dayチケット</t>
   </si>
   <si>
-    <t>伊予铁道市内电车·机场巴士1日票</t>
-  </si>
-  <si>
     <t>/images/coverage/Iyotetsu-City-Tram-Limousine-Bus-1Day.png</t>
   </si>
   <si>
@@ -284,9 +273,6 @@
     <t>電車24時間乗車券～市内均一料金区間版～</t>
   </si>
   <si>
-    <t>土佐电车24小时票（市内均一价格区间版）</t>
-  </si>
-  <si>
     <t>/images/coverage/Tosaden-Densha-24Hr-City-Fare.png</t>
   </si>
   <si>
@@ -305,9 +291,6 @@
     <t>電車24時間乗車券～軌道全線版～</t>
   </si>
   <si>
-    <t>土佐电车24小时票（轨道全线版）</t>
-  </si>
-  <si>
     <t>/images/coverage/Tosaden-Densha-24Hr-Whole-Line.png</t>
   </si>
   <si>
@@ -317,35 +300,20 @@
     <t>/images/coverage/Tosaden-Bus-Tram-1Day-Mobile-Ticket.png</t>
   </si>
   <si>
-    <t>Kurosio-Nahari-Sen-Free-Pass</t>
-  </si>
-  <si>
     <t>ごめん・なはり線フリーきっぷ</t>
   </si>
   <si>
     <t>/images/coverage/Kurosio-Nahari-Sen-Free-Pass.png</t>
   </si>
   <si>
-    <t>Kurosio-1Day-Free-Pass</t>
-  </si>
-  <si>
     <t>くろしお1日フリーきっぷ</t>
-  </si>
-  <si>
-    <t>/images/coverage/Kurosio-1Day-Free-Pass.png</t>
-  </si>
-  <si>
-    <t>Shikoku-Shimanto-Uwakai-Free-Pass</t>
-  </si>
-  <si>
-    <t>/images/coverage/Shikoku-Shimanto-Uwakai-Free-Pass.png</t>
   </si>
   <si>
     <t>四国</t>
     <rPh sb="0" eb="2">
       <t>シコク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -373,8 +341,443 @@
     </r>
   </si>
   <si>
-    <t>１日×2枚</t>
-    <phoneticPr fontId="2"/>
+    <t>ticket_note</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バス・路面電車1日乗車券 モバイルチケット</t>
+  </si>
+  <si>
+    <t>四国绿行周游券</t>
+  </si>
+  <si>
+    <t>琴电·JR转环周游券</t>
+  </si>
+  <si>
+    <t>铁路和巴士周游券</t>
+  </si>
+  <si>
+    <t>八岛四国村·志度线周游券</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">票; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>regional</t>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/ticket/brand/2-3UX</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/ticket/brand/2-3V6</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/smart-eki/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-shikoku-tour.net/tour/detail/1157/ja-JP?deptDate=&amp;trial=1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.tosakuro.com/discounts-tickets</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/smart-eki/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>特急</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; 急行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; 普通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Shimanto-Uwakai-FreeTicket-long</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>/images/coverage/Shimanto-Uwakai-FreeTicket-long.png</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/ticket/kururin.htm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/service_ticket/htm/shikoku/weekend-free.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.jr-eki.com/service_ticket/htm/shikoku/saihakken-re.htm</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>普通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※坐普通电车以外需另外加钱</t>
+    <rPh sb="0" eb="1">
+      <t>zuo</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>kuai chu e</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>che</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>xu</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>jia qian</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>yi wai</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ling wai</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>jia q</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>四国周游券</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>四万十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>宇和海周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>四万十</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>宇和海周游券(高知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+      </rPr>
+      <t>↔︎松山</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <rPh sb="11" eb="12">
+      <t>gao zhi</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>マツヤマ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>周末无限周游券</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>四国再</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>发现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>早</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>鸟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -395,17 +798,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>电电</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>子票</t>
+      <t>电周游券</t>
     </r>
     <r>
       <rPr>
@@ -416,7 +809,7 @@
       </rPr>
       <t>24</t>
     </r>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -437,17 +830,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>电电</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>子票</t>
+      <t>电周游券</t>
     </r>
     <r>
       <rPr>
@@ -458,53 +841,7 @@
       </rPr>
       <t>48</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ticket_note</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>土佐电车1日票（轨道全线版）</t>
-  </si>
-  <si>
-    <t>土佐电车·巴士1日移动票</t>
-  </si>
-  <si>
-    <t>バス・路面電車1日乗車券 モバイルチケット</t>
-  </si>
-  <si>
-    <t>四万十·宇和海乘车券</t>
-  </si>
-  <si>
-    <t>フリー区間	タイプ	大人	小人
-中村・宿毛線(全線)	普通列車	2,080円	1,040円
-中村線(窪川～中村)	特急席
-普通列車	2,600円	1,300円</t>
-  </si>
-  <si>
-    <t>四国周游券</t>
-  </si>
-  <si>
-    <t>四国绿行周游券</t>
-  </si>
-  <si>
-    <t>琴电·JR转环周游券</t>
-  </si>
-  <si>
-    <t>琴平电铁1日周游券</t>
-  </si>
-  <si>
-    <t>铁路和巴士周游券</t>
-  </si>
-  <si>
-    <t>八岛四国村·志度线周游券</t>
-  </si>
-  <si>
-    <t>土佐黑潮线周游券</t>
-  </si>
-  <si>
-    <t>黑潮1日周游券</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -544,11 +881,257 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>日乘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
+      <t>日周游券（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>轨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>版）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>土佐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>周游券（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>轨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>道全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>版）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>土佐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>巴士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
@@ -558,35 +1141,39 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>券（市内均一价格区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color theme="1"/>
-        <rFont val="MS Mincho"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>版）</t>
-    </r>
-    <phoneticPr fontId="2"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/ticket/free_ticket2019/index.html</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -627,11 +1214,193 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">票; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
+      <t>票；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>票</t>
+    </r>
+    <rPh sb="10" eb="11">
+      <t>che nei</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>gou p</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>琴平</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电铁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>琴平温泉附</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>入浴券周游券</t>
+    </r>
+    <rPh sb="4" eb="5">
+      <t>fu dai</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/ticket/kotoden_onsen/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>琴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
@@ -641,13 +1410,68 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>循</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>环</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>周游券</t>
+    </r>
+    <rPh sb="5" eb="6">
+      <t>xun huan</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>现</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>子</t>
+      <t>金</t>
     </r>
     <r>
       <rPr>
@@ -667,17 +1491,67 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>票;；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>站</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>票；</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>车</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/new/2023/rail_limousines/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>这</t>
     </r>
     <r>
       <rPr>
@@ -687,17 +1561,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>站</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>购</t>
+      <t>个套餐中有2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>张</t>
     </r>
     <r>
       <rPr>
@@ -707,21 +1581,569 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>票；</t>
-    </r>
-    <phoneticPr fontId="2"/>
+      <t>票，可以2人用，可以1人用2次</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>zhe ge</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>tao can z</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>you</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>zhang p</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ke yi</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ren</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>yomg</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ke yi</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ren</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>yon</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ci</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/new/2023/reoma_tiket/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>琴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>新Reoma世界套票周游券</t>
+    </r>
+    <rPh sb="11" eb="12">
+      <t>tao p</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://kotoden.quicktrip.jp/buy</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/ticket/quicktrip/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>24h</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>48h</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.kotoden.co.jp/publichtm/kotoden/ticket/shikokumura_ticket/index.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※「坊ちゃん列車」不能坐</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>伊予市内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>郊外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>伊予市内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>巴士</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://mican-app.jp/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.iyotetsu.co.jp/ticket/toku/1day_rail.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.iyotetsu.co.jp/ticket/toku/1day_lim.html</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://ticket.jorudan.co.jp/tosaden/train/ja/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.tosaden.co.jp/train/oneday.php</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>土佐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>日周游券（市内版）</t>
+    </r>
+    <rPh sb="10" eb="11">
+      <t>🕐</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t xml:space="preserve">バン </t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>土佐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>周游券（市内版）</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://ticket.jorudan.co.jp/tosakuro/gns-1d/ja/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://shikokururi.com/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>土佐黑潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>中村・宿毛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1日周游券</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>中村・宿毛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="MS Mincho"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1日周游券(窪川～中村)</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Kurosio-Nahari-Sen-Free-Pass</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nakamura-Sukumo-Line-1-Day-Round-Trip-Ticket</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Nakamura-Sukumo-Line-1-Day-Round-Trip-Ticket-parts</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>/images/coverage/Nakamura-Sukumo-Line-1-Day-Round-Trip-Ticket.png</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>/images/coverage/Nakamura-Sukumo-Line-1-Day-Round-Trip-Ticket-parts.png</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>急行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; 普通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>电车</t>
+    </r>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -752,11 +2174,6 @@
       <color theme="1"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF000000"/>
-      <name val="Hiragino Kaku Gothic ProN"/>
     </font>
     <font>
       <sz val="12"/>
@@ -794,24 +2211,37 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Hiragino Kaku Gothic ProN"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="黒体-簡 ミディアム"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="MS Mincho"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -825,21 +2255,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1180,15 +2614,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD144"/>
+  <dimension ref="A1:AD145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="9" max="9" width="24.5" customWidth="1"/>
     <col min="10" max="10" width="22.83203125" customWidth="1"/>
     <col min="11" max="11" width="19.5" customWidth="1"/>
     <col min="12" max="13" width="16.5" customWidth="1"/>
     <col min="14" max="14" width="35.1640625" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" customWidth="1"/>
+    <col min="21" max="21" width="36.83203125" customWidth="1"/>
+    <col min="22" max="22" width="23.33203125" customWidth="1"/>
+    <col min="23" max="23" width="43" customWidth="1"/>
+    <col min="24" max="24" width="47.1640625" customWidth="1"/>
+    <col min="27" max="27" width="20.1640625" customWidth="1"/>
+    <col min="28" max="28" width="45.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30">
@@ -1217,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -1226,10 +2668,10 @@
         <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N1" t="s">
         <v>25</v>
@@ -1274,884 +2716,1371 @@
         <v>22</v>
       </c>
       <c r="AB1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="5">
+        <v>18000</v>
+      </c>
+      <c r="G2" s="5">
+        <v>9000</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O2" s="3">
+        <v>3</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="5">
+        <v>23000</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" s="3">
+        <v>4</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W3" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4100</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2050</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O4" s="3">
+        <v>3</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5400</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="N5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" s="3">
+        <v>4</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2200</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1100</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="X6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>4</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD6" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12000</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6000</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O7" s="3">
+        <v>1</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="W7" s="7" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" ht="20">
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G2" s="3">
-        <v>9000</v>
-      </c>
-      <c r="N2" s="9" t="s">
+      <c r="X7" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AD7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="5">
+        <v>2400</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1200</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="X8" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1400</v>
+      </c>
+      <c r="G9" s="5">
+        <v>700</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W9" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="O2">
+      <c r="Y9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z9" s="3">
         <v>3</v>
       </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="AD9" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1300</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W10" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2200</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1100</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W11" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="X11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z2">
+      <c r="Y11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>5</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3000</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z12" s="3">
         <v>3</v>
       </c>
-      <c r="AD2" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="20">
-      <c r="B3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="3">
-        <v>23000</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3">
-        <v>4</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="AB12" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD12" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3800</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2300</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2800</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="O13" s="3">
+        <v>1</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="20">
-      <c r="B4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2050</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O4">
+      <c r="S13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z13" s="3">
         <v>3</v>
       </c>
-      <c r="P4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="AD13" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>700</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="20">
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" t="s">
+      <c r="S14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="X14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2700</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4">
+        <v>1350</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="20">
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G6" s="3">
-        <v>6000</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="20">
-      <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="20">
-      <c r="B8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>700</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>23</v>
-      </c>
-      <c r="R8" t="s">
-        <v>24</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="20">
-      <c r="B9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>23</v>
-      </c>
-      <c r="R9" t="s">
-        <v>24</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="20">
-      <c r="B10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-      <c r="P10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" t="s">
-        <v>24</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="20">
-      <c r="B11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3000</v>
-      </c>
-      <c r="M11" t="s">
-        <v>107</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" t="s">
-        <v>24</v>
-      </c>
-      <c r="T11" s="2" t="s">
+      <c r="S15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W15" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" ht="20">
-      <c r="B12" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2800</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" t="s">
-        <v>24</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD12" s="2" t="s">
+    </row>
+    <row r="16" spans="1:30" s="3" customFormat="1" ht="20">
+      <c r="B16" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" ht="20">
-      <c r="B13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G13">
-        <v>700</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-      <c r="P13" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>23</v>
-      </c>
-      <c r="R13" t="s">
-        <v>24</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" ht="20">
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2700</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1350</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>23</v>
-      </c>
-      <c r="R14" t="s">
-        <v>24</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" ht="21">
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2000</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>23</v>
-      </c>
-      <c r="R15" t="s">
-        <v>24</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="21">
-      <c r="B16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>75</v>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="E16" s="4">
         <v>2000</v>
       </c>
-      <c r="G16" s="4">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="3">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W16" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="X16" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4">
         <v>1000</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O16">
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" s="3">
         <v>1</v>
       </c>
-      <c r="P16" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" t="s">
+      <c r="P17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="S17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="X17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2300</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4">
+        <v>1150</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O18" s="3">
+        <v>1</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="X18" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="4">
+        <v>500</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4">
+        <v>250</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O19" s="3">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X19" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD19" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="AD16" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="2:30" ht="20">
-      <c r="B17" s="2" t="s">
+      <c r="C20" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" s="12">
+        <v>600</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4">
+        <v>300</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="2" t="s">
+    </row>
+    <row r="21" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B21" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1150</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O17">
+      <c r="C21" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4">
+        <v>500</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O21" s="3">
         <v>1</v>
       </c>
-      <c r="P17" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" t="s">
+      <c r="P21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="S21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X21" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="AD17" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="2:30" ht="20">
-      <c r="B18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18">
-        <v>500</v>
-      </c>
-      <c r="G18">
-        <v>250</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O18">
+    </row>
+    <row r="22" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B22" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4">
+        <v>600</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W22" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X22" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B23" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1800</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4">
+        <v>900</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O23" s="3">
         <v>1</v>
       </c>
-      <c r="P18" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" t="s">
+      <c r="P23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:30" ht="20">
-      <c r="B19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="S23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E19">
-        <v>600</v>
-      </c>
-      <c r="G19">
-        <v>300</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O19">
+      <c r="V23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W23" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="X23" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2200</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1100</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O24" s="3">
         <v>1</v>
       </c>
-      <c r="P19" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" t="s">
+      <c r="P24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="S24" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X24" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AD19" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="2:30" ht="20">
-      <c r="B20" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G20">
-        <v>500</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O20">
+    </row>
+    <row r="25" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B25" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2080</v>
+      </c>
+      <c r="G25" s="4">
+        <v>1040</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O25" s="3">
         <v>1</v>
       </c>
-      <c r="P20" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>23</v>
-      </c>
-      <c r="R20" t="s">
+      <c r="P25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="S25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AD20" s="2" t="s">
+      <c r="T25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X25" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>3</v>
+      </c>
+      <c r="AD25" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="2:30" ht="20">
-      <c r="B21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G21">
-        <v>600</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O21">
+    <row r="26" spans="2:30" s="3" customFormat="1" ht="20">
+      <c r="B26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E26" s="5">
+        <v>2600</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1300</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O26" s="3">
         <v>1</v>
       </c>
-      <c r="P21" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>23</v>
-      </c>
-      <c r="R21" t="s">
+      <c r="P26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="2:30" ht="20">
-      <c r="B22" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G22">
-        <v>900</v>
-      </c>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-      <c r="P22" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" t="s">
-        <v>24</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="2:30" ht="20">
-      <c r="B23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-      <c r="P23" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>23</v>
-      </c>
-      <c r="R23" t="s">
-        <v>24</v>
-      </c>
-      <c r="T23" s="2" t="s">
+      <c r="S26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X26" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AD23" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="2:30" ht="147">
-      <c r="B24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="N24" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>23</v>
-      </c>
-      <c r="R24" t="s">
-        <v>24</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="2:30" ht="20">
-      <c r="B25" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G25" s="3">
-        <v>2050</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O25">
+      <c r="Z26" s="3">
         <v>3</v>
       </c>
-      <c r="P25" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>23</v>
-      </c>
-      <c r="R25" t="s">
-        <v>24</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="89" spans="11:13">
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-    </row>
-    <row r="91" spans="11:13">
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
+      <c r="AD26" s="4"/>
+    </row>
+    <row r="90" spans="11:13">
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
     </row>
     <row r="92" spans="11:13">
       <c r="K92" s="1"/>
@@ -2418,8 +4347,61 @@
       <c r="L144" s="1"/>
       <c r="M144" s="1"/>
     </row>
+    <row r="145" spans="11:13">
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="1"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="W3" r:id="rId1" xr:uid="{254FFD0D-E14B-AB41-8A1C-CF1FAE5E4079}"/>
+    <hyperlink ref="W2" r:id="rId2" xr:uid="{5CF2DF31-F038-1246-BA19-AF38DFD25D46}"/>
+    <hyperlink ref="X2" r:id="rId3" xr:uid="{307F72E6-DBF5-EA40-B5FC-05A31089AFFD}"/>
+    <hyperlink ref="X3" r:id="rId4" xr:uid="{6A15F626-D6F8-CF4A-92DF-1D7BC33D7ABD}"/>
+    <hyperlink ref="W4" r:id="rId5" xr:uid="{9AF9BDAC-01E0-9F4C-BA7C-FF09714C59B5}"/>
+    <hyperlink ref="X4" r:id="rId6" xr:uid="{18CD9E41-53E0-E544-BE58-7321DD4A8938}"/>
+    <hyperlink ref="W5" r:id="rId7" xr:uid="{C28EE528-5DE4-AF4C-BE9A-6F738B944403}"/>
+    <hyperlink ref="X5" r:id="rId8" xr:uid="{F986A9F8-F114-FE43-AA77-9E690A420253}"/>
+    <hyperlink ref="X6" r:id="rId9" xr:uid="{2383E615-113E-854D-A109-B86E787D7BBF}"/>
+    <hyperlink ref="W6" r:id="rId10" xr:uid="{A5224CC7-73A5-5F4B-AE70-6F0D20615DE3}"/>
+    <hyperlink ref="W7" r:id="rId11" xr:uid="{3A465D8B-B3DD-4D47-9FD9-3641C2D37DE4}"/>
+    <hyperlink ref="X7" r:id="rId12" xr:uid="{1147D6E1-F03A-BC42-8F9D-52607D4BE129}"/>
+    <hyperlink ref="W8" r:id="rId13" xr:uid="{08D99B51-5711-1C40-9D9D-1AEC4DD3173C}"/>
+    <hyperlink ref="X8" r:id="rId14" xr:uid="{15840C0A-C5E2-EC4C-ADBD-3EFDD0771904}"/>
+    <hyperlink ref="W9" r:id="rId15" xr:uid="{E9464B04-5FBD-8543-925B-CA683F9F3C8A}"/>
+    <hyperlink ref="W10" r:id="rId16" xr:uid="{9F42952A-A9AF-5147-B250-37B33F749F9E}"/>
+    <hyperlink ref="X11" r:id="rId17" xr:uid="{D8D13194-3778-DB4A-B93F-19807A067448}"/>
+    <hyperlink ref="W11" r:id="rId18" xr:uid="{E2ED958F-E5E5-0545-A235-45C79CEE377A}"/>
+    <hyperlink ref="W12" r:id="rId19" xr:uid="{57D05A9E-30C4-9748-9CED-E9CC6E85D077}"/>
+    <hyperlink ref="W13" r:id="rId20" xr:uid="{5A77CC41-CC23-174D-AA71-AAC1117DC316}"/>
+    <hyperlink ref="X14" r:id="rId21" xr:uid="{DEB98C8D-AB65-C34A-8B64-A00651E585C9}"/>
+    <hyperlink ref="W14" r:id="rId22" xr:uid="{93A0C273-6342-1D4C-9E26-26CBD75FE3C6}"/>
+    <hyperlink ref="X15" r:id="rId23" xr:uid="{BF65DCB2-656D-0D42-9814-0A3DFD2B495B}"/>
+    <hyperlink ref="W15" r:id="rId24" xr:uid="{5FC1D738-034D-8F43-95FA-5E71FE7C1D02}"/>
+    <hyperlink ref="X16" r:id="rId25" xr:uid="{E4580C0E-5B50-4649-A81A-8D1380183618}"/>
+    <hyperlink ref="W16" r:id="rId26" xr:uid="{70FB0BAF-D61B-A241-9368-1AEC0D05B87F}"/>
+    <hyperlink ref="X17" r:id="rId27" xr:uid="{BF6F3082-4745-4E41-A74D-AF683FDFF1C5}"/>
+    <hyperlink ref="W17" r:id="rId28" xr:uid="{C6E95CCB-C36F-1C4E-A76A-B70D96A02FD9}"/>
+    <hyperlink ref="W18" r:id="rId29" xr:uid="{D22FF599-2D33-AE47-A4CA-9401B5DD7618}"/>
+    <hyperlink ref="X18" r:id="rId30" xr:uid="{E644EE8E-608A-CC4D-A311-A83A797B19A1}"/>
+    <hyperlink ref="X19" r:id="rId31" xr:uid="{5DA73A38-43B2-0F45-8DA3-74D247E8283F}"/>
+    <hyperlink ref="W19" r:id="rId32" xr:uid="{86BACCBF-0140-4A49-85DD-0655E190C8AF}"/>
+    <hyperlink ref="W20" r:id="rId33" xr:uid="{C59EAB5E-6606-6542-B7E7-47F2F1473B4E}"/>
+    <hyperlink ref="X20" r:id="rId34" xr:uid="{8CF34B05-71C8-634D-BF23-0550219DA852}"/>
+    <hyperlink ref="X21" r:id="rId35" xr:uid="{29208690-1CF2-BA44-B3B7-8D9F0B929845}"/>
+    <hyperlink ref="W21" r:id="rId36" xr:uid="{13BB1845-B8B3-1F47-92C5-A657277F88E7}"/>
+    <hyperlink ref="W22" r:id="rId37" xr:uid="{83109138-49A3-AD4D-A6D5-68942B34CDE3}"/>
+    <hyperlink ref="X22" r:id="rId38" xr:uid="{FA6621BC-D6CE-3C4E-9F9A-2E3D93522C25}"/>
+    <hyperlink ref="W23" r:id="rId39" xr:uid="{50053E06-9DD1-9D41-8466-7D54357C363B}"/>
+    <hyperlink ref="X23" r:id="rId40" xr:uid="{88A22396-6136-674E-A195-437FF5B6F70D}"/>
+    <hyperlink ref="X24" r:id="rId41" xr:uid="{C6E8A2B5-E320-804D-8B84-A22DE8648514}"/>
+    <hyperlink ref="W24" r:id="rId42" xr:uid="{43B0B245-392E-C14D-BDAB-F5A207BEC3E6}"/>
+    <hyperlink ref="W25" r:id="rId43" xr:uid="{918E4D20-6024-AA47-97AD-7329248C5091}"/>
+    <hyperlink ref="X25" r:id="rId44" xr:uid="{BCCD2814-8653-9B43-9AC8-4466A30CD86F}"/>
+    <hyperlink ref="W26" r:id="rId45" xr:uid="{46CB99AF-84D9-0D41-988D-2FF2AEB26853}"/>
+    <hyperlink ref="X26" r:id="rId46" xr:uid="{11AEB1F0-073A-0549-8A85-1149CFFF526D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>